--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8784"/>
+  <dimension ref="A1:B8796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70708,6 +70708,102 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8785">
+      <c r="A8785" s="2" t="n">
+        <v>46040</v>
+      </c>
+      <c r="B8785" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8786">
+      <c r="A8786" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B8786" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8787">
+      <c r="A8787" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B8787" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8788">
+      <c r="A8788" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B8788" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8789">
+      <c r="A8789" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B8789" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8790">
+      <c r="A8790" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B8790" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8791">
+      <c r="A8791" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B8791" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8792">
+      <c r="A8792" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B8792" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8793">
+      <c r="A8793" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B8793" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8794">
+      <c r="A8794" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B8794" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8795">
+      <c r="A8795" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B8795" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8796">
+      <c r="A8796" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B8796" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8796"/>
+  <dimension ref="A1:B8801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70804,6 +70804,46 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8797">
+      <c r="A8797" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B8797" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8798">
+      <c r="A8798" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B8798" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8799">
+      <c r="A8799" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B8799" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8800">
+      <c r="A8800" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B8800" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8801">
+      <c r="A8801" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B8801" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8801"/>
+  <dimension ref="A1:B8802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70844,6 +70844,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8802">
+      <c r="A8802" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B8802" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8802"/>
+  <dimension ref="A1:B8808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70852,6 +70852,54 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8803">
+      <c r="A8803" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B8803" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8804">
+      <c r="A8804" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B8804" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8805">
+      <c r="A8805" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B8805" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8806">
+      <c r="A8806" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="B8806" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8807">
+      <c r="A8807" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B8807" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8808">
+      <c r="A8808" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B8808" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8808"/>
+  <dimension ref="A1:B8809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70900,6 +70900,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8809">
+      <c r="A8809" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B8809" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8809"/>
+  <dimension ref="A1:B8810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70908,6 +70908,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8810">
+      <c r="A8810" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B8810" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8810"/>
+  <dimension ref="A1:B8811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70916,6 +70916,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8811">
+      <c r="A8811" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B8811" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8811"/>
+  <dimension ref="A1:B8815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70924,6 +70924,38 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8812">
+      <c r="A8812" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B8812" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8813">
+      <c r="A8813" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="B8813" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8814">
+      <c r="A8814" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B8814" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8815">
+      <c r="A8815" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B8815" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8815"/>
+  <dimension ref="A1:B8816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70956,6 +70956,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8816">
+      <c r="A8816" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B8816" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8821"/>
+  <dimension ref="A1:B8828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70992,6 +70992,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8822">
+      <c r="A8822" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B8822" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8823">
+      <c r="A8823" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B8823" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8824">
+      <c r="A8824" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B8824" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8825">
+      <c r="A8825" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B8825" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8826">
+      <c r="A8826" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B8826" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8827">
+      <c r="A8827" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B8827" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8828">
+      <c r="A8828" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B8828" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8828"/>
+  <dimension ref="A1:B8835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71048,6 +71048,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8829">
+      <c r="A8829" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B8829" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8830">
+      <c r="A8830" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B8830" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8831">
+      <c r="A8831" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B8831" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8832">
+      <c r="A8832" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B8832" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8833">
+      <c r="A8833" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B8833" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8834">
+      <c r="A8834" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B8834" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8835">
+      <c r="A8835" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B8835" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8835"/>
+  <dimension ref="A1:B8842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71104,6 +71104,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8836">
+      <c r="A8836" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B8836" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8837">
+      <c r="A8837" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B8837" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8838">
+      <c r="A8838" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B8838" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8839">
+      <c r="A8839" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B8839" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8840">
+      <c r="A8840" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B8840" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8841">
+      <c r="A8841" s="1" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B8841" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8842">
+      <c r="A8842" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B8842" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8842"/>
+  <dimension ref="A1:B8849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71160,6 +71160,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8843">
+      <c r="A8843" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B8843" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8844">
+      <c r="A8844" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B8844" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8845">
+      <c r="A8845" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B8845" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8846">
+      <c r="A8846" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B8846" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8847">
+      <c r="A8847" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B8847" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8848">
+      <c r="A8848" s="1" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B8848" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8849">
+      <c r="A8849" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B8849" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8849"/>
+  <dimension ref="A1:B8856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71216,6 +71216,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8850">
+      <c r="A8850" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B8850" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8851">
+      <c r="A8851" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B8851" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8852">
+      <c r="A8852" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B8852" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8853">
+      <c r="A8853" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B8853" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8854">
+      <c r="A8854" s="1" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B8854" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8855">
+      <c r="A8855" s="1" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B8855" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8856">
+      <c r="A8856" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B8856" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8856"/>
+  <dimension ref="A1:B8863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71272,6 +71272,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8857">
+      <c r="A8857" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B8857" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8858">
+      <c r="A8858" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B8858" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8859">
+      <c r="A8859" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B8859" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8860">
+      <c r="A8860" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B8860" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8861">
+      <c r="A8861" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B8861" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8862">
+      <c r="A8862" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B8862" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8863">
+      <c r="A8863" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B8863" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8863"/>
+  <dimension ref="A1:B8870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71328,6 +71328,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8864">
+      <c r="A8864" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B8864" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8865">
+      <c r="A8865" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B8865" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8866">
+      <c r="A8866" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B8866" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8867">
+      <c r="A8867" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B8867" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8868">
+      <c r="A8868" s="1" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B8868" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8869">
+      <c r="A8869" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B8869" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8870">
+      <c r="A8870" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B8870" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8870"/>
+  <dimension ref="A1:B8877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71384,6 +71384,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8871">
+      <c r="A8871" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B8871" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8872">
+      <c r="A8872" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B8872" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8873">
+      <c r="A8873" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B8873" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8874">
+      <c r="A8874" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B8874" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8875">
+      <c r="A8875" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B8875" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8876">
+      <c r="A8876" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B8876" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8877">
+      <c r="A8877" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B8877" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8877"/>
+  <dimension ref="A1:B8884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71440,6 +71440,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8878">
+      <c r="A8878" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B8878" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8879">
+      <c r="A8879" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B8879" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8880">
+      <c r="A8880" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B8880" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8881">
+      <c r="A8881" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B8881" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8882">
+      <c r="A8882" s="1" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B8882" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8883">
+      <c r="A8883" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B8883" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8884">
+      <c r="A8884" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B8884" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8884"/>
+  <dimension ref="A1:B8891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71496,6 +71496,62 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8885">
+      <c r="A8885" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B8885" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8886">
+      <c r="A8886" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B8886" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8887">
+      <c r="A8887" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B8887" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8888">
+      <c r="A8888" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B8888" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8889">
+      <c r="A8889" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B8889" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8890">
+      <c r="A8890" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B8890" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8891">
+      <c r="A8891" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B8891" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8891"/>
+  <dimension ref="A1:B8919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71552,6 +71552,230 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8892">
+      <c r="A8892" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B8892" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8893">
+      <c r="A8893" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B8893" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8894">
+      <c r="A8894" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B8894" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8895">
+      <c r="A8895" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B8895" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8896">
+      <c r="A8896" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B8896" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8897">
+      <c r="A8897" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B8897" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8898">
+      <c r="A8898" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B8898" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8899">
+      <c r="A8899" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B8899" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8900">
+      <c r="A8900" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B8900" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8901">
+      <c r="A8901" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B8901" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8902">
+      <c r="A8902" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B8902" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8903">
+      <c r="A8903" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B8903" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8904">
+      <c r="A8904" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B8904" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8905">
+      <c r="A8905" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B8905" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8906">
+      <c r="A8906" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B8906" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8907">
+      <c r="A8907" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B8907" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8908">
+      <c r="A8908" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B8908" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8909">
+      <c r="A8909" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B8909" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8910">
+      <c r="A8910" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B8910" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8911">
+      <c r="A8911" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B8911" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8912">
+      <c r="A8912" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B8912" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8913">
+      <c r="A8913" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B8913" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8914">
+      <c r="A8914" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B8914" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8915">
+      <c r="A8915" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B8915" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8916">
+      <c r="A8916" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B8916" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8917">
+      <c r="A8917" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B8917" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8918">
+      <c r="A8918" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B8918" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8919">
+      <c r="A8919" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B8919" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8919"/>
+  <dimension ref="A1:B8949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71277,7 +71277,7 @@
         <v>46112</v>
       </c>
       <c r="B8857" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8858">
@@ -71285,7 +71285,7 @@
         <v>46113</v>
       </c>
       <c r="B8858" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8859">
@@ -71293,7 +71293,7 @@
         <v>46114</v>
       </c>
       <c r="B8859" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8860">
@@ -71301,7 +71301,7 @@
         <v>46115</v>
       </c>
       <c r="B8860" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8861">
@@ -71309,7 +71309,7 @@
         <v>46116</v>
       </c>
       <c r="B8861" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8862">
@@ -71317,7 +71317,7 @@
         <v>46117</v>
       </c>
       <c r="B8862" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8863">
@@ -71325,7 +71325,7 @@
         <v>46118</v>
       </c>
       <c r="B8863" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8864">
@@ -71333,7 +71333,7 @@
         <v>46119</v>
       </c>
       <c r="B8864" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8865">
@@ -71341,7 +71341,7 @@
         <v>46120</v>
       </c>
       <c r="B8865" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8866">
@@ -71349,7 +71349,7 @@
         <v>46121</v>
       </c>
       <c r="B8866" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8867">
@@ -71357,7 +71357,7 @@
         <v>46122</v>
       </c>
       <c r="B8867" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8868">
@@ -71365,7 +71365,7 @@
         <v>46123</v>
       </c>
       <c r="B8868" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8869">
@@ -71373,7 +71373,7 @@
         <v>46124</v>
       </c>
       <c r="B8869" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8870">
@@ -71381,7 +71381,7 @@
         <v>46125</v>
       </c>
       <c r="B8870" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8871">
@@ -71389,7 +71389,7 @@
         <v>46126</v>
       </c>
       <c r="B8871" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8872">
@@ -71397,7 +71397,7 @@
         <v>46127</v>
       </c>
       <c r="B8872" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8873">
@@ -71405,7 +71405,7 @@
         <v>46128</v>
       </c>
       <c r="B8873" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8874">
@@ -71413,7 +71413,7 @@
         <v>46129</v>
       </c>
       <c r="B8874" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8875">
@@ -71421,7 +71421,7 @@
         <v>46130</v>
       </c>
       <c r="B8875" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8876">
@@ -71429,7 +71429,7 @@
         <v>46131</v>
       </c>
       <c r="B8876" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8877">
@@ -71437,7 +71437,7 @@
         <v>46132</v>
       </c>
       <c r="B8877" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8878">
@@ -71445,7 +71445,7 @@
         <v>46133</v>
       </c>
       <c r="B8878" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8879">
@@ -71453,7 +71453,7 @@
         <v>46134</v>
       </c>
       <c r="B8879" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8880">
@@ -71461,7 +71461,7 @@
         <v>46135</v>
       </c>
       <c r="B8880" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8881">
@@ -71469,7 +71469,7 @@
         <v>46136</v>
       </c>
       <c r="B8881" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8882">
@@ -71477,7 +71477,7 @@
         <v>46137</v>
       </c>
       <c r="B8882" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8883">
@@ -71485,7 +71485,7 @@
         <v>46138</v>
       </c>
       <c r="B8883" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8884">
@@ -71493,7 +71493,7 @@
         <v>46139</v>
       </c>
       <c r="B8884" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8885">
@@ -71501,7 +71501,7 @@
         <v>46140</v>
       </c>
       <c r="B8885" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8886">
@@ -71509,7 +71509,7 @@
         <v>46141</v>
       </c>
       <c r="B8886" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8887">
@@ -71517,7 +71517,7 @@
         <v>46142</v>
       </c>
       <c r="B8887" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8888">
@@ -71525,7 +71525,7 @@
         <v>46143</v>
       </c>
       <c r="B8888" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8889">
@@ -71533,7 +71533,7 @@
         <v>46144</v>
       </c>
       <c r="B8889" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8890">
@@ -71541,7 +71541,7 @@
         <v>46145</v>
       </c>
       <c r="B8890" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8891">
@@ -71549,7 +71549,7 @@
         <v>46146</v>
       </c>
       <c r="B8891" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8892">
@@ -71557,7 +71557,7 @@
         <v>46147</v>
       </c>
       <c r="B8892" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8893">
@@ -71565,7 +71565,7 @@
         <v>46148</v>
       </c>
       <c r="B8893" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8894">
@@ -71573,7 +71573,7 @@
         <v>46149</v>
       </c>
       <c r="B8894" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8895">
@@ -71581,7 +71581,7 @@
         <v>46150</v>
       </c>
       <c r="B8895" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8896">
@@ -71589,7 +71589,7 @@
         <v>46151</v>
       </c>
       <c r="B8896" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8897">
@@ -71597,7 +71597,7 @@
         <v>46152</v>
       </c>
       <c r="B8897" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8898">
@@ -71605,7 +71605,7 @@
         <v>46153</v>
       </c>
       <c r="B8898" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8899">
@@ -71613,7 +71613,7 @@
         <v>46154</v>
       </c>
       <c r="B8899" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8900">
@@ -71621,7 +71621,7 @@
         <v>46155</v>
       </c>
       <c r="B8900" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8901">
@@ -71629,7 +71629,7 @@
         <v>46156</v>
       </c>
       <c r="B8901" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8902">
@@ -71637,7 +71637,7 @@
         <v>46157</v>
       </c>
       <c r="B8902" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8903">
@@ -71645,7 +71645,7 @@
         <v>46158</v>
       </c>
       <c r="B8903" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8904">
@@ -71653,7 +71653,7 @@
         <v>46159</v>
       </c>
       <c r="B8904" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8905">
@@ -71661,7 +71661,7 @@
         <v>46160</v>
       </c>
       <c r="B8905" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8906">
@@ -71669,7 +71669,7 @@
         <v>46161</v>
       </c>
       <c r="B8906" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8907">
@@ -71677,7 +71677,7 @@
         <v>46162</v>
       </c>
       <c r="B8907" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8908">
@@ -71685,7 +71685,7 @@
         <v>46163</v>
       </c>
       <c r="B8908" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8909">
@@ -71693,7 +71693,7 @@
         <v>46164</v>
       </c>
       <c r="B8909" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8910">
@@ -71701,7 +71701,7 @@
         <v>46165</v>
       </c>
       <c r="B8910" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8911">
@@ -71709,7 +71709,7 @@
         <v>46166</v>
       </c>
       <c r="B8911" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8912">
@@ -71717,7 +71717,7 @@
         <v>46167</v>
       </c>
       <c r="B8912" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8913">
@@ -71725,7 +71725,7 @@
         <v>46168</v>
       </c>
       <c r="B8913" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8914">
@@ -71733,7 +71733,7 @@
         <v>46169</v>
       </c>
       <c r="B8914" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8915">
@@ -71741,7 +71741,7 @@
         <v>46170</v>
       </c>
       <c r="B8915" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8916">
@@ -71749,7 +71749,7 @@
         <v>46171</v>
       </c>
       <c r="B8916" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8917">
@@ -71757,7 +71757,7 @@
         <v>46172</v>
       </c>
       <c r="B8917" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8918">
@@ -71765,7 +71765,7 @@
         <v>46173</v>
       </c>
       <c r="B8918" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8919">
@@ -71773,7 +71773,247 @@
         <v>46174</v>
       </c>
       <c r="B8919" t="n">
-        <v>28</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8920">
+      <c r="A8920" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B8920" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8921">
+      <c r="A8921" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B8921" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8922">
+      <c r="A8922" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B8922" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8923">
+      <c r="A8923" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B8923" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8924">
+      <c r="A8924" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B8924" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8925">
+      <c r="A8925" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B8925" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8926">
+      <c r="A8926" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B8926" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8927">
+      <c r="A8927" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B8927" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8928">
+      <c r="A8928" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B8928" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8929">
+      <c r="A8929" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B8929" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8930">
+      <c r="A8930" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B8930" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8931">
+      <c r="A8931" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B8931" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8932">
+      <c r="A8932" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B8932" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8933">
+      <c r="A8933" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B8933" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8934">
+      <c r="A8934" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B8934" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8935">
+      <c r="A8935" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B8935" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8936">
+      <c r="A8936" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B8936" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8937">
+      <c r="A8937" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B8937" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8938">
+      <c r="A8938" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B8938" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8939">
+      <c r="A8939" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B8939" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8940">
+      <c r="A8940" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B8940" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8941">
+      <c r="A8941" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B8941" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8942">
+      <c r="A8942" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B8942" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8943">
+      <c r="A8943" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B8943" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8944">
+      <c r="A8944" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B8944" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8945">
+      <c r="A8945" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B8945" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8946">
+      <c r="A8946" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B8946" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8947">
+      <c r="A8947" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B8947" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8948">
+      <c r="A8948" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B8948" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8949">
+      <c r="A8949" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B8949" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8949"/>
+  <dimension ref="A1:B8980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72016,6 +72016,254 @@
         <v>27</v>
       </c>
     </row>
+    <row r="8950">
+      <c r="A8950" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B8950" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8951">
+      <c r="A8951" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B8951" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8952">
+      <c r="A8952" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B8952" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8953">
+      <c r="A8953" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B8953" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8954">
+      <c r="A8954" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B8954" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8955">
+      <c r="A8955" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B8955" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8956">
+      <c r="A8956" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B8956" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8957">
+      <c r="A8957" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B8957" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8958">
+      <c r="A8958" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B8958" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8959">
+      <c r="A8959" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B8959" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8960">
+      <c r="A8960" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B8960" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8961">
+      <c r="A8961" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B8961" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8962">
+      <c r="A8962" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B8962" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8963">
+      <c r="A8963" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B8963" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8964">
+      <c r="A8964" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B8964" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8965">
+      <c r="A8965" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B8965" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8966">
+      <c r="A8966" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B8966" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8967">
+      <c r="A8967" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B8967" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8968">
+      <c r="A8968" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B8968" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8969">
+      <c r="A8969" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B8969" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8970">
+      <c r="A8970" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B8970" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8971">
+      <c r="A8971" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B8971" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8972">
+      <c r="A8972" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B8972" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8973">
+      <c r="A8973" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B8973" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8974">
+      <c r="A8974" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B8974" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8975">
+      <c r="A8975" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B8975" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8976">
+      <c r="A8976" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B8976" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8977">
+      <c r="A8977" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B8977" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8978">
+      <c r="A8978" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B8978" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8979">
+      <c r="A8979" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8979" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8980">
+      <c r="A8980" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B8980" t="n">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8980"/>
+  <dimension ref="A1:B8997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72264,6 +72264,142 @@
         <v>27</v>
       </c>
     </row>
+    <row r="8981">
+      <c r="A8981" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B8981" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8982">
+      <c r="A8982" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B8982" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8983">
+      <c r="A8983" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B8983" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8984">
+      <c r="A8984" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B8984" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8985">
+      <c r="A8985" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B8985" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8986">
+      <c r="A8986" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B8986" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8987">
+      <c r="A8987" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B8987" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8988">
+      <c r="A8988" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B8988" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8989">
+      <c r="A8989" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B8989" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8990">
+      <c r="A8990" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B8990" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8991">
+      <c r="A8991" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B8991" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8992">
+      <c r="A8992" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B8992" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8993">
+      <c r="A8993" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B8993" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8994">
+      <c r="A8994" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B8994" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8995">
+      <c r="A8995" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B8995" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8996">
+      <c r="A8996" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B8996" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8997">
+      <c r="A8997" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B8997" t="n">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
